--- a/Exemplos_Codigo_STM32/calculoTimer.xlsx
+++ b/Exemplos_Codigo_STM32/calculoTimer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BACKUP_LOCAL\AULAS FATEC\MICROCONTORLADORES\2025_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\GIT_AULAS_FATEC\Exemplos_Codigo_STM32\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EBFE0B-9DA8-457B-AE4A-29E4D8149DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2384EBDF-9A70-46B6-B978-16D3F72476D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0F553953-7539-41EE-9D73-D6F519E96D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F553953-7539-41EE-9D73-D6F519E96D34}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Calculo Timer 1</t>
   </si>
@@ -45,21 +45,12 @@
     <t>Prescaler</t>
   </si>
   <si>
-    <t>Contador</t>
-  </si>
-  <si>
     <t>Fosc(MHz)</t>
   </si>
   <si>
     <t>Fosc(Hz)</t>
   </si>
   <si>
-    <t>Preíodo da interrupção por estouro</t>
-  </si>
-  <si>
-    <t>Frequncia da interrupçao por estouro</t>
-  </si>
-  <si>
     <t>Vin</t>
   </si>
   <si>
@@ -73,6 +64,24 @@
   </si>
   <si>
     <t>Ganho</t>
+  </si>
+  <si>
+    <t>ARR</t>
+  </si>
+  <si>
+    <t>Periodo por count</t>
+  </si>
+  <si>
+    <t>Periodo Estouro</t>
+  </si>
+  <si>
+    <t>Frequencia</t>
+  </si>
+  <si>
+    <t>Tempo que eu quero</t>
+  </si>
+  <si>
+    <t>Numero de counts</t>
   </si>
 </sst>
 </file>
@@ -124,7 +133,7 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -140,35 +149,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -211,9 +192,20 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -221,9 +213,20 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -233,22 +236,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,81 +593,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432F2CC5-A964-4EB5-A8D8-F3E958E3BF7D}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4">
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
         <v>72</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="12">
         <f>B3*1000000</f>
         <v>72000000</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="E3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="15">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="8">
-        <f>1/(C3/(B4+1))*(B5+1)</f>
-        <v>9.9749999999999999E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="8">
-        <f>1/D8</f>
-        <v>10025.062656641605</v>
-      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="E4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="13">
+        <f>F3/B6</f>
+        <v>1080000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>65535</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <f>1/(C3/B4)</f>
+        <v>1.3888888888888889E-8</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <f>B6*B5</f>
+        <v>9.1020833333333329E-4</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="11">
+        <f>1/B7</f>
+        <v>1098.6495765621423</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B8:C8"/>
+  <mergeCells count="1">
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -674,7 +750,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1">
         <v>5</v>
@@ -682,7 +758,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <f>(1+(B4/B3))*B1</f>
@@ -691,7 +767,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>1000000</v>
@@ -699,7 +775,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>120</v>
@@ -707,7 +783,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <f>1+(B4/B3)</f>

--- a/Exemplos_Codigo_STM32/calculoTimer.xlsx
+++ b/Exemplos_Codigo_STM32/calculoTimer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\GIT_AULAS_FATEC\Exemplos_Codigo_STM32\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2384EBDF-9A70-46B6-B978-16D3F72476D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D5D98C-E2A4-4468-B453-EA518DF69E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F553953-7539-41EE-9D73-D6F519E96D34}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0F553953-7539-41EE-9D73-D6F519E96D34}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -236,22 +236,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -259,6 +254,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432F2CC5-A964-4EB5-A8D8-F3E958E3BF7D}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -614,21 +612,21 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>72</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="9">
         <f>B3*1000000</f>
         <v>72000000</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="15">
-        <v>1.4999999999999999E-2</v>
+      <c r="F3" s="12">
+        <v>0.01</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -636,15 +634,14 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="E4" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="10">
         <f>F3/B6</f>
-        <v>1080000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -652,9 +649,8 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>65535</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>1000</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -662,75 +658,33 @@
       </c>
       <c r="B6" s="2">
         <f>1/(C3/B4)</f>
-        <v>1.3888888888888889E-8</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>9.9999999999999995E-7</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="2">
         <f>B6*B5</f>
-        <v>9.1020833333333329E-4</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+        <v>1E-3</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="8">
         <f>1/B7</f>
-        <v>1098.6495765621423</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+        <v>1000</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Exemplos_Codigo_STM32/calculoTimer.xlsx
+++ b/Exemplos_Codigo_STM32/calculoTimer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\GIT_AULAS_FATEC\Exemplos_Codigo_STM32\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D5D98C-E2A4-4468-B453-EA518DF69E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0558DB17-D31F-4BE5-843B-6C940CF9E37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0F553953-7539-41EE-9D73-D6F519E96D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F553953-7539-41EE-9D73-D6F519E96D34}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
